--- a/alicea_ranking_chart.xlsx
+++ b/alicea_ranking_chart.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -567,14 +567,13 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1822,7 +1821,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C2A8C99E-ECC6-45B0-9838-754AD8176E34}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C2A8C99E-ECC6-45B0-9838-754AD8176E34}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A1:B14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField showAll="0"/>
@@ -2263,7 +2262,7 @@
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>288553.14</v>
       </c>
     </row>
@@ -2271,7 +2270,7 @@
       <c r="A3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>302862.71000000002</v>
       </c>
     </row>
@@ -2279,7 +2278,7 @@
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>304732.76</v>
       </c>
     </row>
@@ -2287,7 +2286,7 @@
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>306998.14</v>
       </c>
     </row>
@@ -2295,7 +2294,7 @@
       <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>310389.02</v>
       </c>
     </row>
@@ -2303,7 +2302,7 @@
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>311520.52</v>
       </c>
     </row>
@@ -2311,7 +2310,7 @@
       <c r="A8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>313920.05</v>
       </c>
     </row>
@@ -2319,7 +2318,7 @@
       <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9">
         <v>313971.65000000002</v>
       </c>
     </row>
@@ -2327,7 +2326,7 @@
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B10">
         <v>314979.99</v>
       </c>
     </row>
@@ -2335,7 +2334,7 @@
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B11">
         <v>334175.88</v>
       </c>
     </row>
@@ -2343,7 +2342,7 @@
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12">
         <v>607148.21</v>
       </c>
     </row>
@@ -2351,7 +2350,7 @@
       <c r="A13" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B13" s="4">
+      <c r="B13">
         <v>621565.02</v>
       </c>
     </row>
@@ -2359,7 +2358,7 @@
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="4">
+      <c r="B14">
         <v>4330817.09</v>
       </c>
       <c r="O14" s="3"/>
